--- a/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_vol/staggered_7d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_vol/staggered_7d/close/close_annual_metrics.xlsx
@@ -466,18 +466,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1461814957575758</v>
+        <v>0.1026436356253566</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.1716777627579777</v>
+        <v>0.1271714234532442</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3148974173526969</v>
+        <v>0.2487156612854152</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2594966060581725</v>
+        <v>0.1861504433519763</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.5991085284622402</v>
+        <v>0.5081378913929785</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.8791242372762235</v>
+        <v>0.7244612657379932</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.818005840447535</v>
+        <v>0.8057668839581241</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.216399410391994</v>
+        <v>0.1850160901437667</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1656722219859791</v>
+        <v>0.104965967111412</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.7703322478251222</v>
+        <v>0.6309940883340835</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>23.42253728404914</v>
+        <v>26.68263464621009</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1950004194038585</v>
+        <v>-0.1919693982456487</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.03948362649906167</v>
+        <v>0.04339753768793475</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2745363654008641</v>
+        <v>0.2434248413606647</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1849033226183626</v>
+        <v>0.149828626228221</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.7398947981528583</v>
+        <v>-0.8510696324494105</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.01378724135863</v>
+        <v>-1.13686048034818</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.3036490146944136</v>
+        <v>0.3477456307010448</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2697743552941875</v>
+        <v>0.25049726620197</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1447943446580688</v>
+        <v>0.1045857628495807</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.749454802702712</v>
+        <v>-0.7946407584211428</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>23.78554239584734</v>
+        <v>24.87997766642475</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1739442299040143</v>
+        <v>-0.1491707578122843</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.06747830774617136</v>
+        <v>-0.03951191497429174</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.238506913500844</v>
+        <v>0.2008938092329911</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1742933229932912</v>
+        <v>0.1303908630007685</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.7779396651228903</v>
+        <v>-0.8112710915004137</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-1.117613488096678</v>
+        <v>-1.139462252682089</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.3073300581995923</v>
+        <v>-0.2377538414860376</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.2891085204757026</v>
+        <v>0.2802640734385571</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1486952862888831</v>
+        <v>0.1208226057959498</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.6241303928637291</v>
+        <v>-0.5524483992419174</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>27.16405436572394</v>
+        <v>27.02448320901361</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.08053650763126885</v>
+        <v>-0.007449277371460172</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.1861766060331945</v>
+        <v>-0.1214866011778216</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2963697571495984</v>
+        <v>0.2488451637109056</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1580321545161202</v>
+        <v>0.1286684221365441</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.1993738296617979</v>
+        <v>0.03133177270140262</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.3115564564758815</v>
+        <v>0.05032785792747534</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.246222764981176</v>
+        <v>-1.010800729590879</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2665845623578291</v>
+        <v>0.2509860081733153</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2143589670746271</v>
+        <v>0.1847490622231672</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.3140510949605311</v>
+        <v>-0.03090173055462906</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>26.02509198285641</v>
+        <v>26.53069328456679</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3194318447583846</v>
+        <v>0.2415922654760847</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.07768516542069714</v>
+        <v>0.01410737608025214</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2957994270655745</v>
+        <v>0.2225221123760482</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1790324005687684</v>
+        <v>0.1098353643106384</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.069755755010333</v>
+        <v>1.053437238317387</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.567792230625332</v>
+        <v>1.497196020259506</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.5994044678379817</v>
+        <v>0.2302788454451089</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1804399514508989</v>
+        <v>0.1658946930070463</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1460505275845929</v>
+        <v>0.1229812684707997</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.845754473941985</v>
+        <v>1.516523100128605</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>27.09721285393724</v>
+        <v>28.5569190497931</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.2184686662315825</v>
+        <v>0.2090632119048106</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.237076064853514</v>
+        <v>0.2275269785707246</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.3648555898984417</v>
+        <v>0.2893345911541583</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2401445149898416</v>
+        <v>0.1709548192944067</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.131238371196349</v>
+        <v>1.291590720619799</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.587630324516113</v>
+        <v>1.846233229278196</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.786684196865721</v>
+        <v>2.281454488130549</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1294734251041985</v>
+        <v>0.1191751188049011</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1025937274063009</v>
+        <v>0.06686715443346447</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.35600156358138</v>
+        <v>3.476875408537367</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>23.91277265175547</v>
+        <v>27.22817543350884</v>
       </c>
     </row>
   </sheetData>
